--- a/TIMES-NZ/v303/VT_TIMESNZ_TRA.xlsx
+++ b/TIMES-NZ/v303/VT_TIMESNZ_TRA.xlsx
@@ -2613,7 +2613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P401"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8036,30 +8036,35 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
+          <t>AFA~2024</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
           <t>INVCOST</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t>FIXOM</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
+      <c r="N205" t="inlineStr">
         <is>
           <t>PRC_resid~2023</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
+      <c r="O205" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
+      <c r="P205" t="inlineStr">
         <is>
           <t>Share~0</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr">
+      <c r="Q205" t="inlineStr">
         <is>
           <t>CEFF</t>
         </is>
@@ -8118,15 +8123,20 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
+      <c r="N206" t="inlineStr">
         <is>
           <t>696.3727933333333</t>
         </is>
@@ -8185,15 +8195,20 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
+      <c r="N207" t="inlineStr">
         <is>
           <t>257.56254</t>
         </is>
@@ -8252,15 +8267,20 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="N208" t="inlineStr">
         <is>
           <t>696.3727933333333</t>
         </is>
@@ -8319,15 +8339,20 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
+      <c r="N209" t="inlineStr">
         <is>
           <t>257.56254</t>
         </is>
@@ -8386,15 +8411,20 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
+      <c r="N210" t="inlineStr">
         <is>
           <t>696.3727933333333</t>
         </is>
@@ -8453,15 +8483,20 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
           <t>37.90695415695416</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t>6.697393672993671e-05</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="N211" t="inlineStr">
         <is>
           <t>257.56254</t>
         </is>
@@ -8520,15 +8555,20 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
+      <c r="N212" t="inlineStr">
         <is>
           <t>74.82791999999999</t>
         </is>
@@ -8587,15 +8627,20 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="N213" t="inlineStr">
         <is>
           <t>27.67608</t>
         </is>
@@ -8654,15 +8699,20 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
+      <c r="N214" t="inlineStr">
         <is>
           <t>74.82791999999999</t>
         </is>
@@ -8721,15 +8771,20 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
+      <c r="N215" t="inlineStr">
         <is>
           <t>27.67608</t>
         </is>
@@ -8788,15 +8843,20 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
+      <c r="N216" t="inlineStr">
         <is>
           <t>74.82791999999999</t>
         </is>
@@ -8855,15 +8915,20 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
           <t>53.56537943537943</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t>8.921429804763139e-05</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
+      <c r="N217" t="inlineStr">
         <is>
           <t>27.67608</t>
         </is>
@@ -8922,15 +8987,20 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
+      <c r="N218" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -8989,15 +9059,20 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
+      <c r="N219" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9056,15 +9131,20 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
+      <c r="N220" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -9123,15 +9203,20 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
+      <c r="N221" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9190,15 +9275,20 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
+      <c r="N222" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -9257,15 +9347,20 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
+      <c r="N223" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9324,15 +9419,20 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
+      <c r="N224" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -9391,15 +9491,20 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
+      <c r="N225" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9458,15 +9563,20 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="N226" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -9525,15 +9635,20 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
+      <c r="N227" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9592,15 +9707,20 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="N228" t="inlineStr">
         <is>
           <t>17.393223333333335</t>
         </is>
@@ -9659,15 +9779,20 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
           <t>48.08721315721317</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t>6.066215130548461e-05</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
+      <c r="N229" t="inlineStr">
         <is>
           <t>6.43311</t>
         </is>
@@ -9726,15 +9851,20 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
+      <c r="N230" t="inlineStr">
         <is>
           <t>0.1374833333333333</t>
         </is>
@@ -9793,15 +9923,20 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
+      <c r="N231" t="inlineStr">
         <is>
           <t>0.05085</t>
         </is>
@@ -9860,15 +9995,20 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="N232" t="inlineStr">
         <is>
           <t>0.1374833333333333</t>
         </is>
@@ -9927,15 +10067,20 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr">
+      <c r="N233" t="inlineStr">
         <is>
           <t>0.05085</t>
         </is>
@@ -9994,15 +10139,20 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
+      <c r="N234" t="inlineStr">
         <is>
           <t>0.1374833333333333</t>
         </is>
@@ -10061,15 +10211,20 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
           <t>60.83560174545436</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>0.0001637186426799</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr">
+      <c r="N235" t="inlineStr">
         <is>
           <t>0.05085</t>
         </is>
@@ -10128,15 +10283,20 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr">
+      <c r="N236" t="inlineStr">
         <is>
           <t>69.50281333333334</t>
         </is>
@@ -10195,15 +10355,20 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr">
+      <c r="N237" t="inlineStr">
         <is>
           <t>25.70652</t>
         </is>
@@ -10262,15 +10427,20 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr">
+      <c r="N238" t="inlineStr">
         <is>
           <t>69.50281333333334</t>
         </is>
@@ -10329,15 +10499,20 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
+      <c r="N239" t="inlineStr">
         <is>
           <t>25.70652</t>
         </is>
@@ -10396,15 +10571,20 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
+      <c r="N240" t="inlineStr">
         <is>
           <t>69.50281333333334</t>
         </is>
@@ -10463,15 +10643,20 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
           <t>42.201445221445226</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t>7.254144929144931e-05</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr">
+      <c r="N241" t="inlineStr">
         <is>
           <t>25.70652</t>
         </is>
@@ -10530,20 +10715,25 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
+      <c r="N242" t="inlineStr">
         <is>
           <t>3.075538666666666</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr">
+      <c r="O242" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -10602,20 +10792,25 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
+      <c r="N243" t="inlineStr">
         <is>
           <t>4.613308</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr">
+      <c r="O243" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -10674,20 +10869,25 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
+      <c r="N244" t="inlineStr">
         <is>
           <t>1.137528</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr">
+      <c r="O244" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -10746,20 +10946,25 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
+      <c r="N245" t="inlineStr">
         <is>
           <t>1.706292</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr">
+      <c r="O245" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -10818,20 +11023,25 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
+      <c r="N246" t="inlineStr">
         <is>
           <t>3.075538666666666</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr">
+      <c r="O246" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -10890,20 +11100,25 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
+      <c r="N247" t="inlineStr">
         <is>
           <t>4.613308</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr">
+      <c r="O247" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -10962,20 +11177,25 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
+      <c r="N248" t="inlineStr">
         <is>
           <t>1.137528</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr">
+      <c r="O248" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -11034,20 +11254,25 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
+      <c r="N249" t="inlineStr">
         <is>
           <t>1.706292</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr">
+      <c r="O249" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -11106,20 +11331,25 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr">
+      <c r="N250" t="inlineStr">
         <is>
           <t>3.075538666666666</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr">
+      <c r="O250" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -11178,20 +11408,25 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="N251" t="inlineStr">
         <is>
           <t>4.613308</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr">
+      <c r="O251" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -11250,20 +11485,25 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
+      <c r="N252" t="inlineStr">
         <is>
           <t>1.137528</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr">
+      <c r="O252" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
@@ -11322,20 +11562,25 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
           <t>52.06540533540534</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>7.72617094017094e-05</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
+      <c r="N253" t="inlineStr">
         <is>
           <t>1.706292</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr">
+      <c r="O253" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
@@ -11394,15 +11639,20 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
+      <c r="N254" t="inlineStr">
         <is>
           <t>37.03533333333333</t>
         </is>
@@ -11461,15 +11711,20 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
+      <c r="N255" t="inlineStr">
         <is>
           <t>13.698</t>
         </is>
@@ -11528,15 +11783,20 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="M256" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr">
+      <c r="N256" t="inlineStr">
         <is>
           <t>37.03533333333333</t>
         </is>
@@ -11595,15 +11855,20 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr">
+      <c r="N257" t="inlineStr">
         <is>
           <t>13.698</t>
         </is>
@@ -11662,15 +11927,20 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="M258" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
+      <c r="N258" t="inlineStr">
         <is>
           <t>37.03533333333333</t>
         </is>
@@ -11729,15 +11999,20 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
           <t>60.64460502460503</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t>4.7054467014467e-05</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr">
+      <c r="N259" t="inlineStr">
         <is>
           <t>13.698</t>
         </is>
@@ -11796,15 +12071,20 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="M260" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
+      <c r="N260" t="inlineStr">
         <is>
           <t>148.35644</t>
         </is>
@@ -11863,15 +12143,20 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="M261" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr">
+      <c r="N261" t="inlineStr">
         <is>
           <t>54.87156000000001</t>
         </is>
@@ -11930,15 +12215,20 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="M262" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr">
+      <c r="N262" t="inlineStr">
         <is>
           <t>148.35644</t>
         </is>
@@ -11997,15 +12287,20 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="M263" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
+      <c r="N263" t="inlineStr">
         <is>
           <t>54.87156000000001</t>
         </is>
@@ -12064,15 +12359,20 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="M264" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr">
+      <c r="N264" t="inlineStr">
         <is>
           <t>148.35644</t>
         </is>
@@ -12131,15 +12431,20 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
           <t>56.728368298368295</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="M265" t="inlineStr">
         <is>
           <t>8.411090790690789e-05</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
+      <c r="N265" t="inlineStr">
         <is>
           <t>54.87156000000001</t>
         </is>
@@ -12198,15 +12503,20 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="M266" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
+      <c r="N266" t="inlineStr">
         <is>
           <t>0.4435966666666666</t>
         </is>
@@ -12265,15 +12575,20 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
+      <c r="M267" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
+      <c r="N267" t="inlineStr">
         <is>
           <t>0.16407</t>
         </is>
@@ -12332,15 +12647,20 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr">
+      <c r="N268" t="inlineStr">
         <is>
           <t>0.4435966666666666</t>
         </is>
@@ -12399,15 +12719,20 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="M269" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
+      <c r="N269" t="inlineStr">
         <is>
           <t>0.16407</t>
         </is>
@@ -12466,15 +12791,20 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="M270" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
+      <c r="N270" t="inlineStr">
         <is>
           <t>0.4435966666666666</t>
         </is>
@@ -12533,15 +12863,20 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
           <t>70.91290598290598</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="M271" t="inlineStr">
         <is>
           <t>4.66827343027343e-05</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
+      <c r="N271" t="inlineStr">
         <is>
           <t>0.16407</t>
         </is>
@@ -12600,15 +12935,20 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="M272" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
+      <c r="N272" t="inlineStr">
         <is>
           <t>0.0659433333333333</t>
         </is>
@@ -12667,15 +13007,20 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
+      <c r="N273" t="inlineStr">
         <is>
           <t>0.02439</t>
         </is>
@@ -12734,15 +13079,20 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="M274" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
+      <c r="N274" t="inlineStr">
         <is>
           <t>0.0659433333333333</t>
         </is>
@@ -12801,15 +13151,20 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
+      <c r="N275" t="inlineStr">
         <is>
           <t>0.02439</t>
         </is>
@@ -12868,15 +13223,20 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="M276" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
+      <c r="N276" t="inlineStr">
         <is>
           <t>0.0659433333333333</t>
         </is>
@@ -12935,15 +13295,20 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
           <t>70.36443152992518</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t>0.00015413497601</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
+      <c r="N277" t="inlineStr">
         <is>
           <t>0.02439</t>
         </is>
@@ -13002,15 +13367,20 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr">
+      <c r="N278" t="inlineStr">
         <is>
           <t>49.96533666666667</t>
         </is>
@@ -13069,15 +13439,20 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="M279" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
+      <c r="N279" t="inlineStr">
         <is>
           <t>18.48033</t>
         </is>
@@ -13136,15 +13511,20 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="M280" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="N280" t="inlineStr">
         <is>
           <t>49.96533666666667</t>
         </is>
@@ -13203,15 +13583,20 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
+      <c r="N281" t="inlineStr">
         <is>
           <t>18.48033</t>
         </is>
@@ -13270,15 +13655,20 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
+      <c r="N282" t="inlineStr">
         <is>
           <t>49.96533666666667</t>
         </is>
@@ -13337,15 +13727,20 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
           <t>4.890241647241648</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="M283" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr">
+      <c r="N283" t="inlineStr">
         <is>
           <t>18.48033</t>
         </is>
@@ -13404,15 +13799,20 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr">
+      <c r="N284" t="inlineStr">
         <is>
           <t>0.6236633333333333</t>
         </is>
@@ -13471,15 +13871,20 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="M285" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
+      <c r="N285" t="inlineStr">
         <is>
           <t>0.23067</t>
         </is>
@@ -13538,15 +13943,20 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
+      <c r="M286" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr">
+      <c r="N286" t="inlineStr">
         <is>
           <t>0.6236633333333333</t>
         </is>
@@ -13605,15 +14015,20 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="M287" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
+      <c r="N287" t="inlineStr">
         <is>
           <t>0.23067</t>
         </is>
@@ -13672,15 +14087,20 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
+      <c r="M288" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
+      <c r="N288" t="inlineStr">
         <is>
           <t>0.6236633333333333</t>
         </is>
@@ -13739,15 +14159,20 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
           <t>8.109642579642578</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr">
+      <c r="N289" t="inlineStr">
         <is>
           <t>0.23067</t>
         </is>
@@ -13806,15 +14231,20 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr">
+      <c r="N290" t="inlineStr">
         <is>
           <t>0.0345533333333333</t>
         </is>
@@ -13873,15 +14303,20 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
+      <c r="M291" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr">
+      <c r="N291" t="inlineStr">
         <is>
           <t>0.01278</t>
         </is>
@@ -13940,15 +14375,20 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
+      <c r="M292" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr">
+      <c r="N292" t="inlineStr">
         <is>
           <t>0.0345533333333333</t>
         </is>
@@ -14007,15 +14447,20 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
+      <c r="M293" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr">
+      <c r="N293" t="inlineStr">
         <is>
           <t>0.01278</t>
         </is>
@@ -14074,15 +14519,20 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
+      <c r="M294" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr">
+      <c r="N294" t="inlineStr">
         <is>
           <t>0.0345533333333333</t>
         </is>
@@ -14141,15 +14591,20 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
+      <c r="M295" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr">
+      <c r="N295" t="inlineStr">
         <is>
           <t>0.01278</t>
         </is>
@@ -14208,15 +14663,20 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
+      <c r="M296" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
+      <c r="N296" t="inlineStr">
         <is>
           <t>2.67253</t>
         </is>
@@ -14275,15 +14735,20 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr">
+      <c r="N297" t="inlineStr">
         <is>
           <t>0.98847</t>
         </is>
@@ -14342,15 +14807,20 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
+      <c r="M298" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr">
+      <c r="N298" t="inlineStr">
         <is>
           <t>2.67253</t>
         </is>
@@ -14409,15 +14879,20 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="M299" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr">
+      <c r="N299" t="inlineStr">
         <is>
           <t>0.98847</t>
         </is>
@@ -14476,15 +14951,20 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
+      <c r="M300" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr">
+      <c r="N300" t="inlineStr">
         <is>
           <t>2.67253</t>
         </is>
@@ -14543,15 +15023,20 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
+      <c r="M301" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr">
+      <c r="N301" t="inlineStr">
         <is>
           <t>0.98847</t>
         </is>
@@ -14610,15 +15095,20 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
+      <c r="M302" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr">
+      <c r="N302" t="inlineStr">
         <is>
           <t>0.00803</t>
         </is>
@@ -14677,15 +15167,20 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
+      <c r="M303" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr">
+      <c r="N303" t="inlineStr">
         <is>
           <t>0.00297</t>
         </is>
@@ -14744,15 +15239,20 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
+      <c r="M304" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr">
+      <c r="N304" t="inlineStr">
         <is>
           <t>0.00803</t>
         </is>
@@ -14811,15 +15311,20 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
+      <c r="M305" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr">
+      <c r="N305" t="inlineStr">
         <is>
           <t>0.00297</t>
         </is>
@@ -14878,15 +15383,20 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
+      <c r="M306" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr">
+      <c r="N306" t="inlineStr">
         <is>
           <t>0.00803</t>
         </is>
@@ -14945,15 +15455,20 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
           <t>393.6802973977696</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
+      <c r="M307" t="inlineStr">
         <is>
           <t>0.0008464126394052</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
+      <c r="N307" t="inlineStr">
         <is>
           <t>0.00297</t>
         </is>
@@ -15012,15 +15527,20 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
+      <c r="M308" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr">
+      <c r="N308" t="inlineStr">
         <is>
           <t>0.08541</t>
         </is>
@@ -15079,15 +15599,20 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="M309" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr">
+      <c r="N309" t="inlineStr">
         <is>
           <t>0.03159</t>
         </is>
@@ -15146,15 +15671,20 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="M310" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr">
+      <c r="N310" t="inlineStr">
         <is>
           <t>0.08541</t>
         </is>
@@ -15213,15 +15743,20 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="M311" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr">
+      <c r="N311" t="inlineStr">
         <is>
           <t>0.03159</t>
         </is>
@@ -15280,15 +15815,20 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
+      <c r="M312" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr">
+      <c r="N312" t="inlineStr">
         <is>
           <t>0.08541</t>
         </is>
@@ -15347,15 +15887,20 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
           <t>576.413404739777</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
+      <c r="M313" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr">
+      <c r="N313" t="inlineStr">
         <is>
           <t>0.03159</t>
         </is>
@@ -15414,15 +15959,20 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
+      <c r="M314" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
+      <c r="N314" t="inlineStr">
         <is>
           <t>0.5779166666666666</t>
         </is>
@@ -15481,15 +16031,20 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="M315" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
+      <c r="N315" t="inlineStr">
         <is>
           <t>0.21375</t>
         </is>
@@ -15548,15 +16103,20 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
+      <c r="M316" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
+      <c r="N316" t="inlineStr">
         <is>
           <t>0.5779166666666666</t>
         </is>
@@ -15615,15 +16175,20 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="M317" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="N317" t="inlineStr">
         <is>
           <t>0.21375</t>
         </is>
@@ -15682,15 +16247,20 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="M318" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="N318" t="inlineStr">
         <is>
           <t>0.5779166666666666</t>
         </is>
@@ -15749,15 +16319,20 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="M319" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="N319" t="inlineStr">
         <is>
           <t>0.21375</t>
         </is>
@@ -15816,15 +16391,20 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr">
+      <c r="N320" t="inlineStr">
         <is>
           <t>21.86277</t>
         </is>
@@ -15883,15 +16463,20 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="M321" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="N321" t="inlineStr">
         <is>
           <t>8.08623</t>
         </is>
@@ -15950,15 +16535,20 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
+      <c r="M322" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr">
+      <c r="N322" t="inlineStr">
         <is>
           <t>21.86277</t>
         </is>
@@ -16017,15 +16607,20 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr">
+      <c r="N323" t="inlineStr">
         <is>
           <t>8.08623</t>
         </is>
@@ -16084,15 +16679,20 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="M324" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
+      <c r="N324" t="inlineStr">
         <is>
           <t>21.86277</t>
         </is>
@@ -16151,15 +16751,20 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
           <t>78.24395910780669</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="M325" t="inlineStr">
         <is>
           <t>0.0001366263360013</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr">
+      <c r="N325" t="inlineStr">
         <is>
           <t>8.08623</t>
         </is>
@@ -16218,15 +16823,20 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
+      <c r="M326" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr">
+      <c r="N326" t="inlineStr">
         <is>
           <t>0.0279833333333333</t>
         </is>
@@ -16285,15 +16895,20 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr">
+      <c r="N327" t="inlineStr">
         <is>
           <t>0.01035</t>
         </is>
@@ -16352,15 +16967,20 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr">
+      <c r="N328" t="inlineStr">
         <is>
           <t>0.0279833333333333</t>
         </is>
@@ -16419,15 +17039,20 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr">
+      <c r="N329" t="inlineStr">
         <is>
           <t>0.01035</t>
         </is>
@@ -16486,15 +17111,20 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
+      <c r="M330" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr">
+      <c r="N330" t="inlineStr">
         <is>
           <t>0.0279833333333333</t>
         </is>
@@ -16553,15 +17183,20 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
           <t>126.27131505576207</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="M331" t="inlineStr">
         <is>
           <t>8.79966227101303e-05</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="N331" t="inlineStr">
         <is>
           <t>0.01035</t>
         </is>
@@ -16620,15 +17255,20 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr">
+      <c r="N332" t="inlineStr">
         <is>
           <t>11.079696666666663</t>
         </is>
@@ -16687,15 +17327,20 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
+      <c r="M333" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
+      <c r="N333" t="inlineStr">
         <is>
           <t>4.097970000000001</t>
         </is>
@@ -16754,15 +17399,20 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
+      <c r="M334" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr">
+      <c r="N334" t="inlineStr">
         <is>
           <t>11.079696666666663</t>
         </is>
@@ -16821,15 +17471,20 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
+      <c r="M335" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr">
+      <c r="N335" t="inlineStr">
         <is>
           <t>4.097970000000001</t>
         </is>
@@ -16888,15 +17543,20 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
+      <c r="M336" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr">
+      <c r="N336" t="inlineStr">
         <is>
           <t>11.079696666666663</t>
         </is>
@@ -16955,15 +17615,20 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
           <t>175.67983271375465</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
+      <c r="M337" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr">
+      <c r="N337" t="inlineStr">
         <is>
           <t>4.097970000000001</t>
         </is>
@@ -17022,15 +17687,20 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
+      <c r="M338" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M338" t="inlineStr">
+      <c r="N338" t="inlineStr">
         <is>
           <t>0.01971</t>
         </is>
@@ -17089,15 +17759,20 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
+      <c r="M339" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M339" t="inlineStr">
+      <c r="N339" t="inlineStr">
         <is>
           <t>0.00729</t>
         </is>
@@ -17156,15 +17831,20 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
+      <c r="M340" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr">
+      <c r="N340" t="inlineStr">
         <is>
           <t>0.01971</t>
         </is>
@@ -17223,15 +17903,20 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
+      <c r="M341" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M341" t="inlineStr">
+      <c r="N341" t="inlineStr">
         <is>
           <t>0.00729</t>
         </is>
@@ -17290,15 +17975,20 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
+      <c r="M342" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr">
+      <c r="N342" t="inlineStr">
         <is>
           <t>0.01971</t>
         </is>
@@ -17357,15 +18047,20 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
           <t>381.8075557620818</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
+      <c r="M343" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M343" t="inlineStr">
+      <c r="N343" t="inlineStr">
         <is>
           <t>0.00729</t>
         </is>
@@ -17424,15 +18119,20 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
+      <c r="M344" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr">
+      <c r="N344" t="inlineStr">
         <is>
           <t>8.780683333333334</t>
         </is>
@@ -17491,15 +18191,20 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
+      <c r="M345" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr">
+      <c r="N345" t="inlineStr">
         <is>
           <t>3.24765</t>
         </is>
@@ -17558,15 +18263,20 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
+      <c r="M346" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M346" t="inlineStr">
+      <c r="N346" t="inlineStr">
         <is>
           <t>8.780683333333334</t>
         </is>
@@ -17625,15 +18335,20 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
+      <c r="M347" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr">
+      <c r="N347" t="inlineStr">
         <is>
           <t>3.24765</t>
         </is>
@@ -17692,15 +18407,20 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
+      <c r="M348" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr">
+      <c r="N348" t="inlineStr">
         <is>
           <t>8.780683333333334</t>
         </is>
@@ -17759,15 +18479,20 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
           <t>344.47026022304834</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t>0.000175993246503</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr">
+      <c r="N349" t="inlineStr">
         <is>
           <t>3.24765</t>
         </is>
@@ -17826,15 +18551,20 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
+          <t>0.2175</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="M350" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr">
+      <c r="N350" t="inlineStr">
         <is>
           <t>0.0034066666666666</t>
         </is>
@@ -17893,15 +18623,20 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
+          <t>0.2175</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
+      <c r="M351" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr">
+      <c r="N351" t="inlineStr">
         <is>
           <t>0.00126</t>
         </is>
@@ -17960,15 +18695,20 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
+          <t>0.5655</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
+      <c r="M352" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr">
+      <c r="N352" t="inlineStr">
         <is>
           <t>0.0034066666666666</t>
         </is>
@@ -18027,15 +18767,20 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
+          <t>0.5655</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
+      <c r="M353" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M353" t="inlineStr">
+      <c r="N353" t="inlineStr">
         <is>
           <t>0.00126</t>
         </is>
@@ -18094,15 +18839,20 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
+          <t>0.957</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
+      <c r="M354" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M354" t="inlineStr">
+      <c r="N354" t="inlineStr">
         <is>
           <t>0.0034066666666666</t>
         </is>
@@ -18161,15 +18911,20 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
+          <t>0.957</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
           <t>677.1301115241636</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
+      <c r="M355" t="inlineStr">
         <is>
           <t>0.000113469329569</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr">
+      <c r="N355" t="inlineStr">
         <is>
           <t>0.00126</t>
         </is>
@@ -18211,12 +18966,12 @@
           <t>0.2012336544417711</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="L356" t="inlineStr">
         <is>
           <t>6993.109337062937</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
+      <c r="M356" t="inlineStr">
         <is>
           <t>35459.92270545454</t>
         </is>
@@ -18258,12 +19013,12 @@
           <t>0.3906300350928499</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr">
+      <c r="L357" t="inlineStr">
         <is>
           <t>6993.109337062937</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
+      <c r="M357" t="inlineStr">
         <is>
           <t>35459.92270545454</t>
         </is>
@@ -18305,12 +19060,12 @@
           <t>3.2299096537656</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
+      <c r="L358" t="inlineStr">
         <is>
           <t>6993.109337062937</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
+      <c r="M358" t="inlineStr">
         <is>
           <t>35459.92270545454</t>
         </is>
@@ -18352,12 +19107,12 @@
           <t>1.2560759764644</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
+      <c r="L359" t="inlineStr">
         <is>
           <t>6993.109337062937</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
+      <c r="M359" t="inlineStr">
         <is>
           <t>35459.92270545454</t>
         </is>
@@ -18399,12 +19154,12 @@
           <t>10.756738775580812</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr">
+      <c r="L360" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
+      <c r="M360" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18446,12 +19201,12 @@
           <t>7.789362561627485</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr">
+      <c r="L361" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
+      <c r="M361" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18493,12 +19248,12 @@
           <t>31.328020259186403</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr">
+      <c r="L362" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
+      <c r="M362" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18540,12 +19295,12 @@
           <t>7.832005064796601</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr">
+      <c r="L363" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
+      <c r="M363" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18587,17 +19342,17 @@
           <t>0.3187175540718552</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr">
+      <c r="L364" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
+      <c r="M364" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr">
+      <c r="O364" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
@@ -18639,12 +19394,12 @@
           <t>0.1119818433225437</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr">
+      <c r="L365" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr">
+      <c r="M365" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18686,17 +19441,17 @@
           <t>0.0117607056839999</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr">
+      <c r="L366" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
+      <c r="M366" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
+      <c r="O366" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
@@ -18738,12 +19493,12 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr">
+      <c r="L367" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr">
+      <c r="M367" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18785,17 +19540,17 @@
           <t>0.0401690694363996</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr">
+      <c r="L368" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
+      <c r="M368" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
+      <c r="O368" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
@@ -18837,12 +19592,12 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
+      <c r="L369" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
+      <c r="M369" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -18884,17 +19639,17 @@
           <t>0.11106232426224</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr">
+      <c r="L370" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
+      <c r="M370" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
+      <c r="O370" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
@@ -18936,12 +19691,12 @@
           <t>0.03902189771376</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
+      <c r="L371" t="inlineStr">
         <is>
           <t>888.7058823529412</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
+      <c r="M371" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
